--- a/DataTables/Datas/__enums__.xlsx
+++ b/DataTables/Datas/__enums__.xlsx
@@ -1088,7 +1088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L43"/>
+  <dimension ref="A1:L68"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.85"/>
   <cols>
     <col width="19" customWidth="1" style="5" min="2" max="2"/>
@@ -1284,6 +1284,8 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
+    <row r="9"/>
     <row r="10">
       <c r="B10" s="4" t="inlineStr">
         <is>
@@ -1367,6 +1369,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="B17" s="4" t="inlineStr">
         <is>
@@ -1403,273 +1406,576 @@
       </c>
     </row>
     <row r="19">
-      <c r="H19" s="4" t="n"/>
-      <c r="I19" s="4" t="n"/>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>ReduceDmg</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>减伤</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="H20" s="4" t="n"/>
-      <c r="I20" s="4" t="n"/>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>Chill</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>冰冻</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>RarityEnum</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D21" s="4" t="b">
-        <v>1</v>
-      </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Stun</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>普通</t>
+          <t>晕眩</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Vulnerable</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>稀有</t>
+          <t>易伤</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>ReduceChannel</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>史诗</t>
+          <t>引导缩短</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>Root</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>禁锢</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>DrawCard</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>灵感</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>EffectEnum</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D26" s="4" t="b">
-        <v>1</v>
-      </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>Attack</t>
+          <t>Taunt</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>嘲讽</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>Defense</t>
+          <t>Taunted</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>被嘲讽</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>TimeSlot</t>
+          <t>Stagger</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>破韧</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>Heal</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>格挡</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="H30" s="4" t="inlineStr">
         <is>
+          <t>Strength</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>力量</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>虚弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Frail</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>脆弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Dexterity</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>敏捷</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Regen</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>再生</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Energized</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>充能</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>CardCost</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>减费</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Poison</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>中毒</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Burn</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>燃烧</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Artifact</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>圣物</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="H40" s="4" t="n"/>
+      <c r="I40" s="4" t="n"/>
+    </row>
+    <row r="41">
+      <c r="H41" s="4" t="n"/>
+      <c r="I41" s="4" t="n"/>
+    </row>
+    <row r="42">
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>RarityEnum</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D42" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t>史诗</t>
+        </is>
+      </c>
+    </row>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47">
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>EffectEnum</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D47" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>Defense</t>
+        </is>
+      </c>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>TimeSlot</t>
+        </is>
+      </c>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>Heal</t>
+        </is>
+      </c>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="H51" s="4" t="inlineStr">
+        <is>
           <t>Null</t>
         </is>
       </c>
-      <c r="I30" s="4" t="inlineStr">
+      <c r="I51" s="4" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="H31" s="4" t="inlineStr">
+    <row r="52">
+      <c r="H52" s="4" t="inlineStr">
         <is>
           <t>Buff</t>
         </is>
       </c>
-      <c r="I31" s="4" t="inlineStr">
+      <c r="I52" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="H32" s="4" t="inlineStr">
+    <row r="53">
+      <c r="H53" s="4" t="inlineStr">
         <is>
           <t>Fill</t>
         </is>
       </c>
-      <c r="I32" s="4" t="inlineStr">
+      <c r="I53" s="4" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="B33" s="4" t="n"/>
-      <c r="H33" s="4" t="n"/>
-      <c r="I33" s="4" t="n"/>
-    </row>
-    <row r="34">
-      <c r="H34" s="4" t="n"/>
-      <c r="I34" s="4" t="n"/>
-    </row>
-    <row r="35">
-      <c r="B35" s="4" t="inlineStr">
+    <row r="54">
+      <c r="B54" s="4" t="n"/>
+      <c r="H54" s="4" t="n"/>
+      <c r="I54" s="4" t="n"/>
+    </row>
+    <row r="55">
+      <c r="H55" s="4" t="n"/>
+      <c r="I55" s="4" t="n"/>
+    </row>
+    <row r="56">
+      <c r="B56" s="4" t="inlineStr">
         <is>
           <t>EnemyIntentionEnum</t>
         </is>
       </c>
-      <c r="C35" s="4" t="b">
+      <c r="C56" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="D35" s="4" t="b">
+      <c r="D56" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="H35" s="4" t="inlineStr">
+      <c r="H56" s="4" t="inlineStr">
         <is>
           <t>Attack0</t>
         </is>
       </c>
-      <c r="I35" s="4" t="inlineStr">
+      <c r="I56" s="4" t="inlineStr">
         <is>
           <t>A0</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="H36" s="4" t="inlineStr">
+    <row r="57">
+      <c r="H57" s="4" t="inlineStr">
         <is>
           <t>Attack1</t>
         </is>
       </c>
-      <c r="I36" s="4" t="inlineStr">
+      <c r="I57" s="4" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="H37" s="4" t="inlineStr">
+    <row r="58">
+      <c r="H58" s="4" t="inlineStr">
         <is>
           <t>Attack2</t>
         </is>
       </c>
-      <c r="I37" s="4" t="inlineStr">
+      <c r="I58" s="4" t="inlineStr">
         <is>
           <t>A2</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="H38" s="4" t="inlineStr">
+    <row r="59">
+      <c r="H59" s="4" t="inlineStr">
         <is>
           <t>Skill0</t>
         </is>
       </c>
-      <c r="I38" s="4" t="inlineStr">
+      <c r="I59" s="4" t="inlineStr">
         <is>
           <t>S0</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="H39" s="4" t="inlineStr">
+    <row r="60">
+      <c r="H60" s="4" t="inlineStr">
         <is>
           <t>Skill1</t>
         </is>
       </c>
-      <c r="I39" s="4" t="inlineStr">
+      <c r="I60" s="4" t="inlineStr">
         <is>
           <t>S1</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="B41" t="inlineStr">
+    <row r="61"/>
+    <row r="62">
+      <c r="B62" s="4" t="inlineStr">
         <is>
           <t>CardTypeEnum</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C62" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D62" s="4" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="H42" t="inlineStr">
+    <row r="63">
+      <c r="H63" s="4" t="inlineStr">
         <is>
           <t>Swift</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="I63" s="4" t="inlineStr">
         <is>
           <t>迅捷行动</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="H43" t="inlineStr">
+    <row r="64">
+      <c r="H64" s="4" t="inlineStr">
         <is>
           <t>Execution</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="I64" s="4" t="inlineStr">
         <is>
           <t>执行行动</t>
+        </is>
+      </c>
+    </row>
+    <row r="65"/>
+    <row r="66">
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>BuffPolarityEnum</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D66" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t>增益</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>Debuff</t>
+        </is>
+      </c>
+      <c r="I67" s="4" t="inlineStr">
+        <is>
+          <t>减益</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I68" s="4" t="inlineStr">
+        <is>
+          <t>中性</t>
         </is>
       </c>
     </row>

--- a/DataTables/Datas/__enums__.xlsx
+++ b/DataTables/Datas/__enums__.xlsx
@@ -1088,7 +1088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L68"/>
+  <dimension ref="A1:L74"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.85"/>
   <cols>
     <col width="19" customWidth="1" style="5" min="2" max="2"/>
@@ -1550,432 +1550,503 @@
       </c>
     </row>
     <row r="31">
-      <c r="H31" t="inlineStr">
+      <c r="H31" s="4" t="inlineStr">
         <is>
           <t>Weak</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I31" s="4" t="inlineStr">
         <is>
           <t>虚弱</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="H32" t="inlineStr">
+      <c r="H32" s="4" t="inlineStr">
         <is>
           <t>Frail</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I32" s="4" t="inlineStr">
         <is>
           <t>脆弱</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="H33" t="inlineStr">
+      <c r="H33" s="4" t="inlineStr">
         <is>
           <t>Dexterity</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I33" s="4" t="inlineStr">
         <is>
           <t>敏捷</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="H34" t="inlineStr">
+      <c r="H34" s="4" t="inlineStr">
         <is>
           <t>Regen</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="I34" s="4" t="inlineStr">
         <is>
           <t>再生</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="H35" t="inlineStr">
+      <c r="H35" s="4" t="inlineStr">
         <is>
           <t>Energized</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="I35" s="4" t="inlineStr">
         <is>
           <t>充能</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="H36" t="inlineStr">
+      <c r="H36" s="4" t="inlineStr">
         <is>
           <t>CardCost</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="I36" s="4" t="inlineStr">
         <is>
           <t>减费</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="H37" t="inlineStr">
+      <c r="H37" s="4" t="inlineStr">
         <is>
           <t>Poison</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="I37" s="4" t="inlineStr">
         <is>
           <t>中毒</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="H38" t="inlineStr">
+      <c r="H38" s="4" t="inlineStr">
         <is>
           <t>Burn</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="I38" s="4" t="inlineStr">
         <is>
           <t>燃烧</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="H39" t="inlineStr">
+      <c r="H39" s="4" t="inlineStr">
         <is>
           <t>Artifact</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="I39" s="4" t="inlineStr">
         <is>
           <t>圣物</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="H40" s="4" t="n"/>
-      <c r="I40" s="4" t="n"/>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>Dodge</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>闪避</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="H41" s="4" t="n"/>
       <c r="I41" s="4" t="n"/>
     </row>
     <row r="42">
-      <c r="B42" s="4" t="inlineStr">
+      <c r="H42" s="4" t="n"/>
+      <c r="I42" s="4" t="n"/>
+    </row>
+    <row r="43">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>RarityEnum</t>
         </is>
       </c>
-      <c r="C42" s="4" t="b">
+      <c r="C43" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="D42" s="4" t="b">
+      <c r="D43" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="H42" s="4" t="inlineStr">
+      <c r="H43" s="4" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="I42" s="4" t="inlineStr">
+      <c r="I43" s="4" t="inlineStr">
         <is>
           <t>普通</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="H43" s="4" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="I43" s="4" t="inlineStr">
-        <is>
-          <t>稀有</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="H44" s="4" t="inlineStr">
         <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="H45" s="4" t="inlineStr">
+        <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="I44" s="4" t="inlineStr">
+      <c r="I45" s="4" t="inlineStr">
         <is>
           <t>史诗</t>
         </is>
       </c>
     </row>
-    <row r="45"/>
     <row r="46"/>
-    <row r="47">
-      <c r="B47" s="4" t="inlineStr">
+    <row r="47"/>
+    <row r="48">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>EffectEnum</t>
         </is>
       </c>
-      <c r="C47" s="4" t="b">
+      <c r="C48" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="D47" s="4" t="b">
+      <c r="D48" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="H47" s="4" t="inlineStr">
+      <c r="H48" s="4" t="inlineStr">
         <is>
           <t>Attack</t>
         </is>
       </c>
-      <c r="I47" s="4" t="inlineStr">
+      <c r="I48" s="4" t="inlineStr">
         <is>
           <t>A</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="H48" s="4" t="inlineStr">
-        <is>
-          <t>Defense</t>
-        </is>
-      </c>
-      <c r="I48" s="4" t="inlineStr">
-        <is>
-          <t>D</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>TimeSlot</t>
+          <t>Defense</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>D</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>Heal</t>
+          <t>TimeSlot</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>T</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>Null</t>
+          <t>Heal</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>H</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>Buff</t>
+          <t>Null</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="H53" s="4" t="inlineStr">
         <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="I53" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="H54" s="4" t="inlineStr">
+        <is>
           <t>Fill</t>
         </is>
       </c>
-      <c r="I53" s="4" t="inlineStr">
+      <c r="I54" s="4" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="B54" s="4" t="n"/>
-      <c r="H54" s="4" t="n"/>
-      <c r="I54" s="4" t="n"/>
-    </row>
     <row r="55">
+      <c r="B55" s="4" t="n"/>
       <c r="H55" s="4" t="n"/>
       <c r="I55" s="4" t="n"/>
     </row>
     <row r="56">
-      <c r="B56" s="4" t="inlineStr">
+      <c r="H56" s="4" t="n"/>
+      <c r="I56" s="4" t="n"/>
+    </row>
+    <row r="57">
+      <c r="B57" s="4" t="inlineStr">
         <is>
           <t>EnemyIntentionEnum</t>
         </is>
       </c>
-      <c r="C56" s="4" t="b">
+      <c r="C57" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="D56" s="4" t="b">
+      <c r="D57" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="H56" s="4" t="inlineStr">
+      <c r="H57" s="4" t="inlineStr">
         <is>
           <t>Attack0</t>
         </is>
       </c>
-      <c r="I56" s="4" t="inlineStr">
+      <c r="I57" s="4" t="inlineStr">
         <is>
           <t>A0</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="H57" s="4" t="inlineStr">
-        <is>
-          <t>Attack1</t>
-        </is>
-      </c>
-      <c r="I57" s="4" t="inlineStr">
-        <is>
-          <t>A1</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>Attack2</t>
+          <t>Attack1</t>
         </is>
       </c>
       <c r="I58" s="4" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A1</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>Skill0</t>
+          <t>Attack2</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>S0</t>
+          <t>A2</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="H60" s="4" t="inlineStr">
         <is>
+          <t>Skill0</t>
+        </is>
+      </c>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>S0</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="H61" s="4" t="inlineStr">
+        <is>
           <t>Skill1</t>
         </is>
       </c>
-      <c r="I60" s="4" t="inlineStr">
+      <c r="I61" s="4" t="inlineStr">
         <is>
           <t>S1</t>
         </is>
       </c>
     </row>
-    <row r="61"/>
-    <row r="62">
-      <c r="B62" s="4" t="inlineStr">
+    <row r="62"/>
+    <row r="63">
+      <c r="B63" s="4" t="inlineStr">
         <is>
           <t>CardTypeEnum</t>
         </is>
       </c>
-      <c r="C62" s="4" t="inlineStr">
+      <c r="C63" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="D62" s="4" t="inlineStr">
+      <c r="D63" s="4" t="inlineStr">
         <is>
           <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="H63" s="4" t="inlineStr">
-        <is>
-          <t>Swift</t>
-        </is>
-      </c>
-      <c r="I63" s="4" t="inlineStr">
-        <is>
-          <t>迅捷行动</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="H64" s="4" t="inlineStr">
         <is>
+          <t>Swift</t>
+        </is>
+      </c>
+      <c r="I64" s="4" t="inlineStr">
+        <is>
+          <t>迅捷行动</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="H65" s="4" t="inlineStr">
+        <is>
           <t>Execution</t>
         </is>
       </c>
-      <c r="I64" s="4" t="inlineStr">
+      <c r="I65" s="4" t="inlineStr">
         <is>
           <t>执行行动</t>
         </is>
       </c>
     </row>
-    <row r="65"/>
-    <row r="66">
-      <c r="B66" s="4" t="inlineStr">
+    <row r="66"/>
+    <row r="67">
+      <c r="B67" s="4" t="inlineStr">
         <is>
           <t>BuffPolarityEnum</t>
         </is>
       </c>
-      <c r="C66" s="4" t="b">
+      <c r="C67" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="D66" s="4" t="b">
+      <c r="D67" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="H66" s="4" t="inlineStr">
+      <c r="H67" s="4" t="inlineStr">
         <is>
           <t>Buff</t>
         </is>
       </c>
-      <c r="I66" s="4" t="inlineStr">
+      <c r="I67" s="4" t="inlineStr">
         <is>
           <t>增益</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="H67" s="4" t="inlineStr">
-        <is>
-          <t>Debuff</t>
-        </is>
-      </c>
-      <c r="I67" s="4" t="inlineStr">
-        <is>
-          <t>减益</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="H68" s="4" t="inlineStr">
         <is>
+          <t>Debuff</t>
+        </is>
+      </c>
+      <c r="I68" s="4" t="inlineStr">
+        <is>
+          <t>减益</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="H69" s="4" t="inlineStr">
+        <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="I68" s="4" t="inlineStr">
+      <c r="I69" s="4" t="inlineStr">
         <is>
           <t>中性</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>TargetZoneEnum</t>
+        </is>
+      </c>
+      <c r="C71" t="b">
+        <v>0</v>
+      </c>
+      <c r="D71" t="b">
+        <v>1</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Front</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>前排</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Back</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>后排</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>不限</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Conditional</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>条件</t>
         </is>
       </c>
     </row>

--- a/DataTables/Datas/__enums__.xlsx
+++ b/DataTables/Datas/__enums__.xlsx
@@ -1088,7 +1088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L74"/>
+  <dimension ref="A1:L79"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.85"/>
   <cols>
     <col width="19" customWidth="1" style="5" min="2" max="2"/>
@@ -1670,381 +1670,458 @@
       </c>
     </row>
     <row r="41">
-      <c r="H41" s="4" t="n"/>
-      <c r="I41" s="4" t="n"/>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>Resolve</t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>坚毅</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="H42" s="4" t="n"/>
-      <c r="I42" s="4" t="n"/>
-    </row>
-    <row r="43">
-      <c r="B43" s="4" t="inlineStr">
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>Morale</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>士气</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" s="5">
+      <c r="H43" s="4" t="n"/>
+      <c r="I43" s="4" t="n"/>
+    </row>
+    <row r="44" s="5">
+      <c r="H44" s="4" t="n"/>
+      <c r="I44" s="4" t="n"/>
+    </row>
+    <row r="45">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>RarityEnum</t>
         </is>
       </c>
-      <c r="C43" s="4" t="b">
+      <c r="C45" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="D43" s="4" t="b">
+      <c r="D45" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="H43" s="4" t="inlineStr">
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>Temporary</t>
+        </is>
+      </c>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t>临时</t>
+        </is>
+      </c>
+      <c r="J45" s="4" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="4" t="n"/>
+      <c r="C46" s="4" t="n"/>
+      <c r="D46" s="4" t="n"/>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
+          <t>基础</t>
+        </is>
+      </c>
+      <c r="J46" s="4" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="4" t="n"/>
+      <c r="C47" s="4" t="n"/>
+      <c r="D47" s="4" t="n"/>
+      <c r="H47" s="4" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="I43" s="4" t="inlineStr">
+      <c r="I47" s="4" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-    </row>
-    <row r="44">
-      <c r="H44" s="4" t="inlineStr">
+      <c r="J47" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="H48" s="4" t="inlineStr">
         <is>
           <t>Rare</t>
         </is>
       </c>
-      <c r="I44" s="4" t="inlineStr">
+      <c r="I48" s="4" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-    </row>
-    <row r="45">
-      <c r="H45" s="4" t="inlineStr">
-        <is>
-          <t>Epic</t>
-        </is>
-      </c>
-      <c r="I45" s="4" t="inlineStr">
-        <is>
-          <t>史诗</t>
-        </is>
-      </c>
-    </row>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48">
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>EffectEnum</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D48" s="4" t="b">
+      <c r="J48" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="H48" s="4" t="inlineStr">
-        <is>
-          <t>Attack</t>
-        </is>
-      </c>
-      <c r="I48" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
       </c>
     </row>
     <row r="49">
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>Defense</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="H50" s="4" t="inlineStr">
-        <is>
-          <t>TimeSlot</t>
-        </is>
-      </c>
-      <c r="I50" s="4" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="H51" s="4" t="inlineStr">
-        <is>
-          <t>Heal</t>
-        </is>
-      </c>
-      <c r="I51" s="4" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
+          <t>史诗</t>
+        </is>
+      </c>
+      <c r="J49" s="4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>EffectEnum</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D52" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>Null</t>
+          <t>Attack</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>Buff</t>
+          <t>Defense</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>Fill</t>
+          <t>TimeSlot</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>T</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="B55" s="4" t="n"/>
-      <c r="H55" s="4" t="n"/>
-      <c r="I55" s="4" t="n"/>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>Heal</t>
+        </is>
+      </c>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
     </row>
     <row r="56">
-      <c r="H56" s="4" t="n"/>
-      <c r="I56" s="4" t="n"/>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>Null</t>
+        </is>
+      </c>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="57">
-      <c r="B57" s="4" t="inlineStr">
-        <is>
-          <t>EnemyIntentionEnum</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D57" s="4" t="b">
-        <v>1</v>
-      </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>Attack0</t>
+          <t>Buff</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>A0</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="H58" s="4" t="inlineStr">
         <is>
+          <t>Fill</t>
+        </is>
+      </c>
+      <c r="I58" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="4" t="n"/>
+      <c r="H59" s="4" t="n"/>
+      <c r="I59" s="4" t="n"/>
+    </row>
+    <row r="60">
+      <c r="H60" s="4" t="n"/>
+      <c r="I60" s="4" t="n"/>
+    </row>
+    <row r="61">
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>EnemyIntentionEnum</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D61" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>Attack0</t>
+        </is>
+      </c>
+      <c r="I61" s="4" t="inlineStr">
+        <is>
+          <t>A0</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="H62" s="4" t="inlineStr">
+        <is>
           <t>Attack1</t>
         </is>
       </c>
-      <c r="I58" s="4" t="inlineStr">
+      <c r="I62" s="4" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="H59" s="4" t="inlineStr">
+    <row r="63">
+      <c r="H63" s="4" t="inlineStr">
         <is>
           <t>Attack2</t>
         </is>
       </c>
-      <c r="I59" s="4" t="inlineStr">
+      <c r="I63" s="4" t="inlineStr">
         <is>
           <t>A2</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="H60" s="4" t="inlineStr">
-        <is>
-          <t>Skill0</t>
-        </is>
-      </c>
-      <c r="I60" s="4" t="inlineStr">
-        <is>
-          <t>S0</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="H61" s="4" t="inlineStr">
-        <is>
-          <t>Skill1</t>
-        </is>
-      </c>
-      <c r="I61" s="4" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-    </row>
-    <row r="62"/>
-    <row r="63">
-      <c r="B63" s="4" t="inlineStr">
-        <is>
-          <t>CardTypeEnum</t>
-        </is>
-      </c>
-      <c r="C63" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D63" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>Swift</t>
+          <t>Skill0</t>
         </is>
       </c>
       <c r="I64" s="4" t="inlineStr">
         <is>
-          <t>迅捷行动</t>
+          <t>S0</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Skill1</t>
         </is>
       </c>
       <c r="I65" s="4" t="inlineStr">
         <is>
-          <t>执行行动</t>
-        </is>
-      </c>
-    </row>
-    <row r="66"/>
+          <t>S1</t>
+        </is>
+      </c>
+    </row>
     <row r="67">
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>BuffPolarityEnum</t>
-        </is>
-      </c>
-      <c r="C67" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D67" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H67" s="4" t="inlineStr">
-        <is>
-          <t>Buff</t>
-        </is>
-      </c>
-      <c r="I67" s="4" t="inlineStr">
-        <is>
-          <t>增益</t>
+          <t>CardTypeEnum</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>Debuff</t>
+          <t>Swift</t>
         </is>
       </c>
       <c r="I68" s="4" t="inlineStr">
         <is>
-          <t>减益</t>
+          <t>迅捷行动</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="H69" s="4" t="inlineStr">
         <is>
+          <t>Execution</t>
+        </is>
+      </c>
+      <c r="I69" s="4" t="inlineStr">
+        <is>
+          <t>执行行动</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>Charge</t>
+        </is>
+      </c>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
+          <t>蓄力行动</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>BuffPolarityEnum</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D72" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="I72" s="4" t="inlineStr">
+        <is>
+          <t>增益</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>Debuff</t>
+        </is>
+      </c>
+      <c r="I73" s="4" t="inlineStr">
+        <is>
+          <t>减益</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="H74" s="4" t="inlineStr">
+        <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="I69" s="4" t="inlineStr">
+      <c r="I74" s="4" t="inlineStr">
         <is>
           <t>中性</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="B71" t="inlineStr">
+    <row r="76">
+      <c r="B76" s="4" t="inlineStr">
         <is>
           <t>TargetZoneEnum</t>
         </is>
       </c>
-      <c r="C71" t="b">
+      <c r="C76" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="D71" t="b">
+      <c r="D76" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="H76" s="4" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
+      <c r="I76" s="4" t="inlineStr">
         <is>
           <t>前排</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="H72" t="inlineStr">
+    <row r="77">
+      <c r="H77" s="4" t="inlineStr">
         <is>
           <t>Back</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
+      <c r="I77" s="4" t="inlineStr">
         <is>
           <t>后排</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="H73" t="inlineStr">
+    <row r="78">
+      <c r="H78" s="4" t="inlineStr">
         <is>
           <t>Any</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
+      <c r="I78" s="4" t="inlineStr">
         <is>
           <t>不限</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="H74" t="inlineStr">
+    <row r="79">
+      <c r="H79" s="4" t="inlineStr">
         <is>
           <t>Conditional</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="I79" s="4" t="inlineStr">
         <is>
           <t>条件</t>
         </is>
